--- a/data/raw/inventory/Week 29/Fossil/Seller FBA Inventory (SP-API).xlsx
+++ b/data/raw/inventory/Week 29/Fossil/Seller FBA Inventory (SP-API).xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -17,16 +17,13 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="2">
+  <fonts count="1">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -37,7 +34,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -45,21 +42,12 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -429,82 +417,82 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>SKU</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>ASIN</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>Brand</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>Model</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>Inventory</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>afn_fulfillable_quantity</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>afn_inbound_working_quantity</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>afn_inbound_shipped_quantity</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>afn_inbound_receiving_quantity</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>afn_reserved_quantity</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>afn_total_quantity</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t>afn_unsellable_quantity</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="M1" t="inlineStr">
         <is>
           <t>afn_researching_quantity</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="N1" t="inlineStr">
         <is>
           <t>Seller Account</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="O1" t="inlineStr">
         <is>
           <t>SnapshotDate</t>
         </is>
       </c>
-      <c r="P1" s="1" t="inlineStr">
+      <c r="P1" t="inlineStr">
         <is>
           <t>Week</t>
         </is>
@@ -1152,7 +1140,7 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="F12" t="n">
         <v>5</v>
@@ -1167,10 +1155,10 @@
         <v>0</v>
       </c>
       <c r="J12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K12" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="L12" t="n">
         <v>0</v>
@@ -3632,7 +3620,7 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="F52" t="n">
         <v>15</v>
@@ -3647,10 +3635,10 @@
         <v>0</v>
       </c>
       <c r="J52" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="K52" t="n">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="L52" t="n">
         <v>1</v>
@@ -4131,7 +4119,7 @@
         <v>6</v>
       </c>
       <c r="F60" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G60" t="n">
         <v>0</v>
@@ -4143,7 +4131,7 @@
         <v>0</v>
       </c>
       <c r="J60" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K60" t="n">
         <v>6</v>
@@ -8468,7 +8456,7 @@
         </is>
       </c>
       <c r="E130" t="n">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="F130" t="n">
         <v>99</v>
@@ -8483,10 +8471,10 @@
         <v>0</v>
       </c>
       <c r="J130" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="K130" t="n">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="L130" t="n">
         <v>0</v>
@@ -9463,7 +9451,7 @@
         <v>1</v>
       </c>
       <c r="F146" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G146" t="n">
         <v>0</v>
@@ -9475,7 +9463,7 @@
         <v>0</v>
       </c>
       <c r="J146" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K146" t="n">
         <v>1</v>
@@ -10204,7 +10192,7 @@
         </is>
       </c>
       <c r="E158" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="F158" t="n">
         <v>4</v>
@@ -10219,10 +10207,10 @@
         <v>0</v>
       </c>
       <c r="J158" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K158" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="L158" t="n">
         <v>0</v>
@@ -14792,10 +14780,10 @@
         </is>
       </c>
       <c r="E232" t="n">
-        <v>850</v>
+        <v>851</v>
       </c>
       <c r="F232" t="n">
-        <v>724</v>
+        <v>723</v>
       </c>
       <c r="G232" t="n">
         <v>104</v>
@@ -14807,10 +14795,10 @@
         <v>0</v>
       </c>
       <c r="J232" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="K232" t="n">
-        <v>854</v>
+        <v>855</v>
       </c>
       <c r="L232" t="n">
         <v>4</v>
@@ -17151,7 +17139,7 @@
         <v>106</v>
       </c>
       <c r="F270" t="n">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="G270" t="n">
         <v>0</v>
@@ -17163,7 +17151,7 @@
         <v>0</v>
       </c>
       <c r="J270" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="K270" t="n">
         <v>106</v>
@@ -17337,7 +17325,7 @@
         <v>23</v>
       </c>
       <c r="F273" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="G273" t="n">
         <v>0</v>
@@ -17349,7 +17337,7 @@
         <v>0</v>
       </c>
       <c r="J273" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K273" t="n">
         <v>23</v>
@@ -17396,7 +17384,7 @@
         </is>
       </c>
       <c r="E274" t="n">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="F274" t="n">
         <v>64</v>
@@ -17411,10 +17399,10 @@
         <v>0</v>
       </c>
       <c r="J274" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K274" t="n">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="L274" t="n">
         <v>0</v>
@@ -17585,7 +17573,7 @@
         <v>98</v>
       </c>
       <c r="F277" t="n">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="G277" t="n">
         <v>0</v>
@@ -17597,7 +17585,7 @@
         <v>0</v>
       </c>
       <c r="J277" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K277" t="n">
         <v>99</v>
@@ -17771,7 +17759,7 @@
         <v>251</v>
       </c>
       <c r="F280" t="n">
-        <v>235</v>
+        <v>233</v>
       </c>
       <c r="G280" t="n">
         <v>0</v>
@@ -17783,7 +17771,7 @@
         <v>0</v>
       </c>
       <c r="J280" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="K280" t="n">
         <v>253</v>
@@ -18205,7 +18193,7 @@
         <v>45</v>
       </c>
       <c r="F287" t="n">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="G287" t="n">
         <v>0</v>
@@ -18217,7 +18205,7 @@
         <v>0</v>
       </c>
       <c r="J287" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="K287" t="n">
         <v>45</v>
@@ -18636,7 +18624,7 @@
         </is>
       </c>
       <c r="E294" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="F294" t="n">
         <v>0</v>
@@ -18651,10 +18639,10 @@
         <v>0</v>
       </c>
       <c r="J294" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="K294" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="L294" t="n">
         <v>0</v>
@@ -18887,7 +18875,7 @@
         <v>189</v>
       </c>
       <c r="F298" t="n">
-        <v>187</v>
+        <v>184</v>
       </c>
       <c r="G298" t="n">
         <v>0</v>
@@ -18899,7 +18887,7 @@
         <v>0</v>
       </c>
       <c r="J298" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="K298" t="n">
         <v>189</v>
@@ -18949,7 +18937,7 @@
         <v>7</v>
       </c>
       <c r="F299" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G299" t="n">
         <v>0</v>
@@ -18961,7 +18949,7 @@
         <v>0</v>
       </c>
       <c r="J299" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K299" t="n">
         <v>8</v>
@@ -21736,7 +21724,7 @@
         </is>
       </c>
       <c r="E344" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="F344" t="n">
         <v>7</v>
@@ -21751,10 +21739,10 @@
         <v>0</v>
       </c>
       <c r="J344" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K344" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="L344" t="n">
         <v>0</v>
@@ -22421,7 +22409,7 @@
         <v>6</v>
       </c>
       <c r="F355" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="G355" t="n">
         <v>0</v>
@@ -22433,7 +22421,7 @@
         <v>0</v>
       </c>
       <c r="J355" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K355" t="n">
         <v>6</v>
@@ -25211,7 +25199,7 @@
         <v>7</v>
       </c>
       <c r="F400" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G400" t="n">
         <v>5</v>
@@ -25223,7 +25211,7 @@
         <v>0</v>
       </c>
       <c r="J400" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K400" t="n">
         <v>8</v>
@@ -25397,7 +25385,7 @@
         <v>2</v>
       </c>
       <c r="F403" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G403" t="n">
         <v>0</v>
@@ -25409,7 +25397,7 @@
         <v>0</v>
       </c>
       <c r="J403" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K403" t="n">
         <v>2</v>

--- a/data/raw/inventory/Week 29/Fossil/Seller FBA Inventory (SP-API).xlsx
+++ b/data/raw/inventory/Week 29/Fossil/Seller FBA Inventory (SP-API).xlsx
@@ -771,7 +771,7 @@
         <v>9</v>
       </c>
       <c r="F6" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="G6" t="n">
         <v>0</v>
@@ -783,7 +783,7 @@
         <v>0</v>
       </c>
       <c r="J6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K6" t="n">
         <v>9</v>
@@ -3561,7 +3561,7 @@
         <v>15</v>
       </c>
       <c r="F51" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="G51" t="n">
         <v>3</v>
@@ -3573,7 +3573,7 @@
         <v>0</v>
       </c>
       <c r="J51" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K51" t="n">
         <v>15</v>
@@ -3620,7 +3620,7 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="F52" t="n">
         <v>15</v>
@@ -3635,10 +3635,10 @@
         <v>0</v>
       </c>
       <c r="J52" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="K52" t="n">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="L52" t="n">
         <v>1</v>
@@ -4305,7 +4305,7 @@
         <v>5</v>
       </c>
       <c r="F63" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G63" t="n">
         <v>0</v>
@@ -4317,7 +4317,7 @@
         <v>0</v>
       </c>
       <c r="J63" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K63" t="n">
         <v>5</v>
@@ -5046,7 +5046,7 @@
         </is>
       </c>
       <c r="E75" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="F75" t="n">
         <v>16</v>
@@ -5061,10 +5061,10 @@
         <v>0</v>
       </c>
       <c r="J75" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K75" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="L75" t="n">
         <v>1</v>
@@ -8273,7 +8273,7 @@
         <v>3</v>
       </c>
       <c r="F127" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G127" t="n">
         <v>0</v>
@@ -8285,7 +8285,7 @@
         <v>0</v>
       </c>
       <c r="J127" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K127" t="n">
         <v>3</v>
@@ -13729,7 +13729,7 @@
         <v>3</v>
       </c>
       <c r="F215" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G215" t="n">
         <v>0</v>
@@ -13741,7 +13741,7 @@
         <v>0</v>
       </c>
       <c r="J215" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K215" t="n">
         <v>3</v>
@@ -14780,7 +14780,7 @@
         </is>
       </c>
       <c r="E232" t="n">
-        <v>851</v>
+        <v>852</v>
       </c>
       <c r="F232" t="n">
         <v>723</v>
@@ -14795,10 +14795,10 @@
         <v>0</v>
       </c>
       <c r="J232" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K232" t="n">
-        <v>855</v>
+        <v>856</v>
       </c>
       <c r="L232" t="n">
         <v>4</v>
@@ -17015,7 +17015,7 @@
         <v>27</v>
       </c>
       <c r="F268" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="G268" t="n">
         <v>0</v>
@@ -17027,7 +17027,7 @@
         <v>0</v>
       </c>
       <c r="J268" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K268" t="n">
         <v>27</v>
@@ -17136,10 +17136,10 @@
         </is>
       </c>
       <c r="E270" t="n">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="F270" t="n">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="G270" t="n">
         <v>0</v>
@@ -17151,10 +17151,10 @@
         <v>0</v>
       </c>
       <c r="J270" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="K270" t="n">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="L270" t="n">
         <v>0</v>
@@ -17573,7 +17573,7 @@
         <v>98</v>
       </c>
       <c r="F277" t="n">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="G277" t="n">
         <v>0</v>
@@ -17585,7 +17585,7 @@
         <v>0</v>
       </c>
       <c r="J277" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K277" t="n">
         <v>99</v>
@@ -18872,10 +18872,10 @@
         </is>
       </c>
       <c r="E298" t="n">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="F298" t="n">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="G298" t="n">
         <v>0</v>
@@ -18887,10 +18887,10 @@
         <v>0</v>
       </c>
       <c r="J298" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="K298" t="n">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="L298" t="n">
         <v>0</v>
@@ -19182,10 +19182,10 @@
         </is>
       </c>
       <c r="E303" t="n">
-        <v>869</v>
+        <v>868</v>
       </c>
       <c r="F303" t="n">
-        <v>763</v>
+        <v>759</v>
       </c>
       <c r="G303" t="n">
         <v>72</v>
@@ -19197,10 +19197,10 @@
         <v>0</v>
       </c>
       <c r="J303" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="K303" t="n">
-        <v>873</v>
+        <v>872</v>
       </c>
       <c r="L303" t="n">
         <v>4</v>
@@ -19244,7 +19244,7 @@
         </is>
       </c>
       <c r="E304" t="n">
-        <v>617</v>
+        <v>618</v>
       </c>
       <c r="F304" t="n">
         <v>616</v>
@@ -19259,10 +19259,10 @@
         <v>0</v>
       </c>
       <c r="J304" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K304" t="n">
-        <v>617</v>
+        <v>618</v>
       </c>
       <c r="L304" t="n">
         <v>0</v>
@@ -19430,7 +19430,7 @@
         </is>
       </c>
       <c r="E307" t="n">
-        <v>512</v>
+        <v>513</v>
       </c>
       <c r="F307" t="n">
         <v>407</v>
@@ -19445,10 +19445,10 @@
         <v>0</v>
       </c>
       <c r="J307" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K307" t="n">
-        <v>513</v>
+        <v>514</v>
       </c>
       <c r="L307" t="n">
         <v>1</v>
@@ -20239,7 +20239,7 @@
         <v>20</v>
       </c>
       <c r="F320" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="G320" t="n">
         <v>0</v>
@@ -20251,7 +20251,7 @@
         <v>0</v>
       </c>
       <c r="J320" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K320" t="n">
         <v>20</v>
@@ -22406,7 +22406,7 @@
         </is>
       </c>
       <c r="E355" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="F355" t="n">
         <v>5</v>
@@ -22421,10 +22421,10 @@
         <v>0</v>
       </c>
       <c r="J355" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K355" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="L355" t="n">
         <v>0</v>
@@ -25196,7 +25196,7 @@
         </is>
       </c>
       <c r="E400" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="F400" t="n">
         <v>0</v>
@@ -25211,10 +25211,10 @@
         <v>0</v>
       </c>
       <c r="J400" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K400" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="L400" t="n">
         <v>1</v>

--- a/data/raw/inventory/Week 29/Fossil/Seller FBA Inventory (SP-API).xlsx
+++ b/data/raw/inventory/Week 29/Fossil/Seller FBA Inventory (SP-API).xlsx
@@ -768,10 +768,10 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F6" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="G6" t="n">
         <v>0</v>
@@ -786,7 +786,7 @@
         <v>2</v>
       </c>
       <c r="K6" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="L6" t="n">
         <v>0</v>
@@ -1391,13 +1391,13 @@
         <v>9</v>
       </c>
       <c r="F16" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="G16" t="n">
         <v>0</v>
       </c>
       <c r="H16" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I16" t="n">
         <v>0</v>
@@ -2321,7 +2321,7 @@
         <v>5</v>
       </c>
       <c r="F31" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G31" t="n">
         <v>0</v>
@@ -2333,7 +2333,7 @@
         <v>0</v>
       </c>
       <c r="J31" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K31" t="n">
         <v>5</v>
@@ -2814,10 +2814,10 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F39" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G39" t="n">
         <v>0</v>
@@ -2832,7 +2832,7 @@
         <v>0</v>
       </c>
       <c r="K39" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="L39" t="n">
         <v>0</v>
@@ -3003,7 +3003,7 @@
         <v>14</v>
       </c>
       <c r="F42" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="G42" t="n">
         <v>0</v>
@@ -3015,7 +3015,7 @@
         <v>0</v>
       </c>
       <c r="J42" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K42" t="n">
         <v>14</v>
@@ -3062,11 +3062,11 @@
         </is>
       </c>
       <c r="E43" t="n">
+        <v>19</v>
+      </c>
+      <c r="F43" t="n">
         <v>17</v>
       </c>
-      <c r="F43" t="n">
-        <v>16</v>
-      </c>
       <c r="G43" t="n">
         <v>0</v>
       </c>
@@ -3077,10 +3077,10 @@
         <v>0</v>
       </c>
       <c r="J43" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K43" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="L43" t="n">
         <v>0</v>
@@ -3558,7 +3558,7 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="F51" t="n">
         <v>10</v>
@@ -3573,10 +3573,10 @@
         <v>0</v>
       </c>
       <c r="J51" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K51" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="L51" t="n">
         <v>0</v>
@@ -3620,10 +3620,10 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="F52" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="G52" t="n">
         <v>0</v>
@@ -3635,10 +3635,10 @@
         <v>0</v>
       </c>
       <c r="J52" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="K52" t="n">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="L52" t="n">
         <v>1</v>
@@ -4116,25 +4116,25 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="F60" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G60" t="n">
         <v>0</v>
       </c>
       <c r="H60" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I60" t="n">
         <v>0</v>
       </c>
       <c r="J60" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K60" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="L60" t="n">
         <v>0</v>
@@ -4302,7 +4302,7 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F63" t="n">
         <v>4</v>
@@ -4317,10 +4317,10 @@
         <v>0</v>
       </c>
       <c r="J63" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K63" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="L63" t="n">
         <v>0</v>
@@ -4364,7 +4364,7 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="F64" t="n">
         <v>18</v>
@@ -4379,10 +4379,10 @@
         <v>0</v>
       </c>
       <c r="J64" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K64" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="L64" t="n">
         <v>0</v>
@@ -4491,19 +4491,19 @@
         <v>1</v>
       </c>
       <c r="F66" t="n">
+        <v>0</v>
+      </c>
+      <c r="G66" t="n">
+        <v>0</v>
+      </c>
+      <c r="H66" t="n">
+        <v>0</v>
+      </c>
+      <c r="I66" t="n">
+        <v>0</v>
+      </c>
+      <c r="J66" t="n">
         <v>1</v>
-      </c>
-      <c r="G66" t="n">
-        <v>0</v>
-      </c>
-      <c r="H66" t="n">
-        <v>0</v>
-      </c>
-      <c r="I66" t="n">
-        <v>0</v>
-      </c>
-      <c r="J66" t="n">
-        <v>0</v>
       </c>
       <c r="K66" t="n">
         <v>1</v>
@@ -4869,10 +4869,10 @@
         <v>0</v>
       </c>
       <c r="H72" t="n">
+        <v>0</v>
+      </c>
+      <c r="I72" t="n">
         <v>1</v>
-      </c>
-      <c r="I72" t="n">
-        <v>0</v>
       </c>
       <c r="J72" t="n">
         <v>0</v>
@@ -5170,7 +5170,7 @@
         </is>
       </c>
       <c r="E77" t="n">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="F77" t="n">
         <v>27</v>
@@ -5185,10 +5185,10 @@
         <v>0</v>
       </c>
       <c r="J77" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K77" t="n">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="L77" t="n">
         <v>0</v>
@@ -5294,7 +5294,7 @@
         </is>
       </c>
       <c r="E79" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="F79" t="n">
         <v>7</v>
@@ -5309,10 +5309,10 @@
         <v>0</v>
       </c>
       <c r="J79" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K79" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="L79" t="n">
         <v>0</v>
@@ -5421,13 +5421,13 @@
         <v>27</v>
       </c>
       <c r="F81" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="G81" t="n">
         <v>6</v>
       </c>
       <c r="H81" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="I81" t="n">
         <v>0</v>
@@ -6847,13 +6847,13 @@
         <v>4</v>
       </c>
       <c r="F104" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G104" t="n">
         <v>0</v>
       </c>
       <c r="H104" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I104" t="n">
         <v>0</v>
@@ -7154,10 +7154,10 @@
         </is>
       </c>
       <c r="E109" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F109" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G109" t="n">
         <v>2</v>
@@ -7172,7 +7172,7 @@
         <v>0</v>
       </c>
       <c r="K109" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="L109" t="n">
         <v>0</v>
@@ -8084,7 +8084,7 @@
         </is>
       </c>
       <c r="E124" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F124" t="n">
         <v>3</v>
@@ -8099,10 +8099,10 @@
         <v>0</v>
       </c>
       <c r="J124" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K124" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="L124" t="n">
         <v>0</v>
@@ -8456,28 +8456,28 @@
         </is>
       </c>
       <c r="E130" t="n">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="F130" t="n">
-        <v>99</v>
+        <v>120</v>
       </c>
       <c r="G130" t="n">
         <v>84</v>
       </c>
       <c r="H130" t="n">
-        <v>97</v>
+        <v>44</v>
       </c>
       <c r="I130" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="J130" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K130" t="n">
         <v>283</v>
       </c>
       <c r="L130" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M130" t="n">
         <v>1</v>
@@ -8521,13 +8521,13 @@
         <v>19</v>
       </c>
       <c r="F131" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="G131" t="n">
         <v>3</v>
       </c>
       <c r="H131" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I131" t="n">
         <v>0</v>
@@ -9637,7 +9637,7 @@
         <v>2</v>
       </c>
       <c r="F149" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G149" t="n">
         <v>0</v>
@@ -9649,7 +9649,7 @@
         <v>0</v>
       </c>
       <c r="J149" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K149" t="n">
         <v>2</v>
@@ -10195,13 +10195,13 @@
         <v>13</v>
       </c>
       <c r="F158" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G158" t="n">
         <v>6</v>
       </c>
       <c r="H158" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I158" t="n">
         <v>0</v>
@@ -10440,10 +10440,10 @@
         </is>
       </c>
       <c r="E162" t="n">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="F162" t="n">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="G162" t="n">
         <v>0</v>
@@ -10458,7 +10458,7 @@
         <v>1</v>
       </c>
       <c r="K162" t="n">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="L162" t="n">
         <v>0</v>
@@ -10629,7 +10629,7 @@
         <v>31</v>
       </c>
       <c r="F165" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="G165" t="n">
         <v>7</v>
@@ -10641,7 +10641,7 @@
         <v>0</v>
       </c>
       <c r="J165" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K165" t="n">
         <v>31</v>
@@ -10691,7 +10691,7 @@
         <v>33</v>
       </c>
       <c r="F166" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="G166" t="n">
         <v>0</v>
@@ -10703,7 +10703,7 @@
         <v>2</v>
       </c>
       <c r="J166" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K166" t="n">
         <v>33</v>
@@ -11063,16 +11063,16 @@
         <v>12</v>
       </c>
       <c r="F172" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G172" t="n">
         <v>5</v>
       </c>
       <c r="H172" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="I172" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J172" t="n">
         <v>0</v>
@@ -12805,10 +12805,10 @@
         <v>3</v>
       </c>
       <c r="H200" t="n">
+        <v>0</v>
+      </c>
+      <c r="I200" t="n">
         <v>1</v>
-      </c>
-      <c r="I200" t="n">
-        <v>0</v>
       </c>
       <c r="J200" t="n">
         <v>0</v>
@@ -13239,10 +13239,10 @@
         <v>2</v>
       </c>
       <c r="H207" t="n">
+        <v>0</v>
+      </c>
+      <c r="I207" t="n">
         <v>1</v>
-      </c>
-      <c r="I207" t="n">
-        <v>0</v>
       </c>
       <c r="J207" t="n">
         <v>0</v>
@@ -14411,13 +14411,13 @@
         <v>14</v>
       </c>
       <c r="F226" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="G226" t="n">
         <v>5</v>
       </c>
       <c r="H226" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I226" t="n">
         <v>0</v>
@@ -14535,13 +14535,13 @@
         <v>13</v>
       </c>
       <c r="F228" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="G228" t="n">
         <v>5</v>
       </c>
       <c r="H228" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I228" t="n">
         <v>0</v>
@@ -14780,7 +14780,7 @@
         </is>
       </c>
       <c r="E232" t="n">
-        <v>852</v>
+        <v>851</v>
       </c>
       <c r="F232" t="n">
         <v>723</v>
@@ -14795,10 +14795,10 @@
         <v>0</v>
       </c>
       <c r="J232" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="K232" t="n">
-        <v>856</v>
+        <v>855</v>
       </c>
       <c r="L232" t="n">
         <v>4</v>
@@ -17012,10 +17012,10 @@
         </is>
       </c>
       <c r="E268" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="F268" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="G268" t="n">
         <v>0</v>
@@ -17030,7 +17030,7 @@
         <v>1</v>
       </c>
       <c r="K268" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="L268" t="n">
         <v>0</v>
@@ -17136,10 +17136,10 @@
         </is>
       </c>
       <c r="E270" t="n">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="F270" t="n">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="G270" t="n">
         <v>0</v>
@@ -17154,7 +17154,7 @@
         <v>3</v>
       </c>
       <c r="K270" t="n">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="L270" t="n">
         <v>0</v>
@@ -17201,16 +17201,16 @@
         <v>85</v>
       </c>
       <c r="F271" t="n">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="G271" t="n">
         <v>32</v>
       </c>
       <c r="H271" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="I271" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="J271" t="n">
         <v>1</v>
@@ -17325,7 +17325,7 @@
         <v>23</v>
       </c>
       <c r="F273" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="G273" t="n">
         <v>0</v>
@@ -17337,7 +17337,7 @@
         <v>0</v>
       </c>
       <c r="J273" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K273" t="n">
         <v>23</v>
@@ -17387,7 +17387,7 @@
         <v>65</v>
       </c>
       <c r="F274" t="n">
-        <v>64</v>
+        <v>61</v>
       </c>
       <c r="G274" t="n">
         <v>0</v>
@@ -17399,7 +17399,7 @@
         <v>0</v>
       </c>
       <c r="J274" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="K274" t="n">
         <v>65</v>
@@ -17570,10 +17570,10 @@
         </is>
       </c>
       <c r="E277" t="n">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="F277" t="n">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="G277" t="n">
         <v>0</v>
@@ -17585,10 +17585,10 @@
         <v>0</v>
       </c>
       <c r="J277" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="K277" t="n">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="L277" t="n">
         <v>1</v>
@@ -17756,10 +17756,10 @@
         </is>
       </c>
       <c r="E280" t="n">
-        <v>251</v>
+        <v>247</v>
       </c>
       <c r="F280" t="n">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="G280" t="n">
         <v>0</v>
@@ -17771,16 +17771,16 @@
         <v>0</v>
       </c>
       <c r="J280" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="K280" t="n">
-        <v>253</v>
+        <v>249</v>
       </c>
       <c r="L280" t="n">
         <v>2</v>
       </c>
       <c r="M280" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N280" t="inlineStr">
         <is>
@@ -18190,25 +18190,25 @@
         </is>
       </c>
       <c r="E287" t="n">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="F287" t="n">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="G287" t="n">
         <v>0</v>
       </c>
       <c r="H287" t="n">
+        <v>0</v>
+      </c>
+      <c r="I287" t="n">
+        <v>0</v>
+      </c>
+      <c r="J287" t="n">
         <v>1</v>
       </c>
-      <c r="I287" t="n">
-        <v>0</v>
-      </c>
-      <c r="J287" t="n">
-        <v>3</v>
-      </c>
       <c r="K287" t="n">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="L287" t="n">
         <v>0</v>
@@ -18376,7 +18376,7 @@
         </is>
       </c>
       <c r="E290" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F290" t="n">
         <v>1</v>
@@ -18391,10 +18391,10 @@
         <v>0</v>
       </c>
       <c r="J290" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K290" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="L290" t="n">
         <v>1</v>
@@ -18624,7 +18624,7 @@
         </is>
       </c>
       <c r="E294" t="n">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="F294" t="n">
         <v>0</v>
@@ -18639,10 +18639,10 @@
         <v>0</v>
       </c>
       <c r="J294" t="n">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="K294" t="n">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="L294" t="n">
         <v>0</v>
@@ -18872,25 +18872,25 @@
         </is>
       </c>
       <c r="E298" t="n">
-        <v>188</v>
+        <v>186</v>
       </c>
       <c r="F298" t="n">
+        <v>185</v>
+      </c>
+      <c r="G298" t="n">
+        <v>0</v>
+      </c>
+      <c r="H298" t="n">
+        <v>0</v>
+      </c>
+      <c r="I298" t="n">
+        <v>0</v>
+      </c>
+      <c r="J298" t="n">
+        <v>0</v>
+      </c>
+      <c r="K298" t="n">
         <v>186</v>
-      </c>
-      <c r="G298" t="n">
-        <v>0</v>
-      </c>
-      <c r="H298" t="n">
-        <v>0</v>
-      </c>
-      <c r="I298" t="n">
-        <v>0</v>
-      </c>
-      <c r="J298" t="n">
-        <v>1</v>
-      </c>
-      <c r="K298" t="n">
-        <v>188</v>
       </c>
       <c r="L298" t="n">
         <v>0</v>
@@ -18934,10 +18934,10 @@
         </is>
       </c>
       <c r="E299" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="F299" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G299" t="n">
         <v>0</v>
@@ -18949,10 +18949,10 @@
         <v>0</v>
       </c>
       <c r="J299" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K299" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="L299" t="n">
         <v>1</v>
@@ -19182,7 +19182,7 @@
         </is>
       </c>
       <c r="E303" t="n">
-        <v>868</v>
+        <v>865</v>
       </c>
       <c r="F303" t="n">
         <v>759</v>
@@ -19197,10 +19197,10 @@
         <v>0</v>
       </c>
       <c r="J303" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="K303" t="n">
-        <v>872</v>
+        <v>869</v>
       </c>
       <c r="L303" t="n">
         <v>4</v>
@@ -19244,7 +19244,7 @@
         </is>
       </c>
       <c r="E304" t="n">
-        <v>618</v>
+        <v>616</v>
       </c>
       <c r="F304" t="n">
         <v>616</v>
@@ -19259,10 +19259,10 @@
         <v>0</v>
       </c>
       <c r="J304" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K304" t="n">
-        <v>618</v>
+        <v>616</v>
       </c>
       <c r="L304" t="n">
         <v>0</v>
@@ -19309,13 +19309,13 @@
         <v>7</v>
       </c>
       <c r="F305" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="G305" t="n">
         <v>0</v>
       </c>
       <c r="H305" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I305" t="n">
         <v>0</v>
@@ -19430,10 +19430,10 @@
         </is>
       </c>
       <c r="E307" t="n">
-        <v>513</v>
+        <v>509</v>
       </c>
       <c r="F307" t="n">
-        <v>407</v>
+        <v>404</v>
       </c>
       <c r="G307" t="n">
         <v>84</v>
@@ -19445,13 +19445,13 @@
         <v>0</v>
       </c>
       <c r="J307" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="K307" t="n">
-        <v>514</v>
+        <v>511</v>
       </c>
       <c r="L307" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M307" t="n">
         <v>3</v>
@@ -19681,7 +19681,7 @@
         <v>2</v>
       </c>
       <c r="F311" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G311" t="n">
         <v>0</v>
@@ -19693,7 +19693,7 @@
         <v>0</v>
       </c>
       <c r="J311" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K311" t="n">
         <v>2</v>
@@ -19743,16 +19743,16 @@
         <v>10</v>
       </c>
       <c r="F312" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G312" t="n">
         <v>6</v>
       </c>
       <c r="H312" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I312" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J312" t="n">
         <v>0</v>
@@ -19926,10 +19926,10 @@
         </is>
       </c>
       <c r="E315" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="F315" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="G315" t="n">
         <v>0</v>
@@ -19944,7 +19944,7 @@
         <v>0</v>
       </c>
       <c r="K315" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="L315" t="n">
         <v>0</v>
@@ -20236,7 +20236,7 @@
         </is>
       </c>
       <c r="E320" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="F320" t="n">
         <v>19</v>
@@ -20251,10 +20251,10 @@
         <v>0</v>
       </c>
       <c r="J320" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K320" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="L320" t="n">
         <v>0</v>
@@ -20425,19 +20425,19 @@
         <v>34</v>
       </c>
       <c r="F323" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="G323" t="n">
         <v>19</v>
       </c>
       <c r="H323" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="I323" t="n">
         <v>0</v>
       </c>
       <c r="J323" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K323" t="n">
         <v>34</v>
@@ -20983,13 +20983,13 @@
         <v>13</v>
       </c>
       <c r="F332" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="G332" t="n">
         <v>0</v>
       </c>
       <c r="H332" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="I332" t="n">
         <v>0</v>
@@ -22719,13 +22719,13 @@
         <v>21</v>
       </c>
       <c r="F360" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="G360" t="n">
         <v>4</v>
       </c>
       <c r="H360" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I360" t="n">
         <v>0</v>
@@ -22840,10 +22840,10 @@
         </is>
       </c>
       <c r="E362" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F362" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G362" t="n">
         <v>0</v>
@@ -22858,7 +22858,7 @@
         <v>0</v>
       </c>
       <c r="K362" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="L362" t="n">
         <v>0</v>
@@ -23026,7 +23026,7 @@
         </is>
       </c>
       <c r="E365" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F365" t="n">
         <v>2</v>
@@ -23041,10 +23041,10 @@
         <v>0</v>
       </c>
       <c r="J365" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K365" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="L365" t="n">
         <v>0</v>
@@ -25881,13 +25881,13 @@
         <v>2</v>
       </c>
       <c r="F411" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G411" t="n">
         <v>1</v>
       </c>
       <c r="H411" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I411" t="n">
         <v>0</v>
@@ -25940,7 +25940,7 @@
         </is>
       </c>
       <c r="E412" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="F412" t="n">
         <v>3</v>
@@ -25949,16 +25949,16 @@
         <v>4</v>
       </c>
       <c r="H412" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="I412" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J412" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K412" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="L412" t="n">
         <v>0</v>
@@ -26002,16 +26002,16 @@
         </is>
       </c>
       <c r="E413" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="F413" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="G413" t="n">
         <v>4</v>
       </c>
       <c r="H413" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I413" t="n">
         <v>0</v>
@@ -26020,7 +26020,7 @@
         <v>0</v>
       </c>
       <c r="K413" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="L413" t="n">
         <v>0</v>
